--- a/motor_calculo/referencias_template.xlsx
+++ b/motor_calculo/referencias_template.xlsx
@@ -1597,7 +1597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1610,6 +1610,7 @@
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1663,6 +1664,11 @@
           <t>depende_valor_min</t>
         </is>
       </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
+          <t>unidade</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
@@ -1713,6 +1719,11 @@
       <c r="J2" s="20" t="inlineStr">
         <is>
           <t>Valor real minimo exigido (ex: 100). Deixar em branco = sem dependencia</t>
+        </is>
+      </c>
+      <c r="K2" s="20" t="inlineStr">
+        <is>
+          <t>Opcional: codigo da loja (ex: SAO10) - so preencha pra sobrescrever a regra padrao so nessa loja</t>
         </is>
       </c>
     </row>
